--- a/reports/Debug-snowbowl-20260105/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260105/For The Week Ending (Prior Year)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Snowbowl Tickets</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -476,10 +476,10 @@
         <v>45663</v>
       </c>
       <c r="C5" s="2">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>45663</v>
       </c>
       <c r="C6" s="2">
-        <v>6</v>
+        <v>287</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,7 +504,7 @@
         <v>45663</v>
       </c>
       <c r="C7" s="2">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
